--- a/output/pdf_financials_xlsx/NLH.xlsx
+++ b/output/pdf_financials_xlsx/NLH.xlsx
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.8516089999999999</v>
+        <v>-0.8516089999999999</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.489519</v>
+        <v>-0.489519</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.8516089999999999</v>
+        <v>-0.8516089999999999</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-1.040588</v>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.8516089999999999</v>
+        <v>-0.8516089999999999</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.489519</v>
+        <v>-0.489519</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.8516089999999999</v>
+        <v>-0.8516089999999999</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.961271</v>
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.8516089999999999</v>
+        <v>-0.8516089999999999</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.489519</v>
+        <v>-0.489519</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.8516089999999999</v>
+        <v>-0.8516089999999999</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-0.961271</v>
@@ -1525,13 +1525,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-21.290225</v>
+        <v>21.290225</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-12.237975</v>
+        <v>12.237975</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-21.290225</v>
+        <v>21.290225</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>48.06355</v>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.854739</v>
+        <v>-0.848479</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.490414</v>
+        <v>-0.488624</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.848479</v>
+        <v>-0.854739</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.040588</v>
@@ -1656,13 +1656,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.89033</v>
+        <v>-0.8128880000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.493658</v>
+        <v>-0.48538</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.88407</v>
+        <v>-0.819148</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.5978599999999999</v>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>243.3260453675868</v>
+        <v>-222.1612462421427</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3197.059775921248</v>
+        <v>-3143.449258467716</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -1752,13 +1752,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-9.202969859348753</v>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>232.7436458048647</v>
+        <v>-232.7436458048647</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>3170.254517194483</v>
+        <v>-3170.254517194483</v>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
@@ -30304,10 +30304,10 @@
         </is>
       </c>
       <c r="G373" s="5" t="n">
-        <v>0.8516089999999999</v>
+        <v>-0.8516089999999999</v>
       </c>
       <c r="H373" s="5" t="n">
-        <v>0.961271</v>
+        <v>-0.961271</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -33018,10 +33018,10 @@
         </is>
       </c>
       <c r="E415" s="5" t="n">
-        <v>0.8516089999999999</v>
+        <v>-0.8516089999999999</v>
       </c>
       <c r="F415" s="5" t="n">
-        <v>0.489519</v>
+        <v>-0.489519</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NLH.xlsx
+++ b/output/pdf_financials_xlsx/NLH.xlsx
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.035591</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.003244</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0.035591</v>
@@ -21228,7 +21228,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E235" s="5" t="n">
@@ -22610,7 +22610,11 @@
           <t>Amortization of intangible assets (note</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E256" s="5" t="n">
         <v>4e-06</v>
       </c>
